--- a/InputData/trans/FpUCD/Fare per Unit Cargo Dist.xlsx
+++ b/InputData/trans/FpUCD/Fare per Unit Cargo Dist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28712"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-mexico\InputData\trans\FpUCD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/skorpius/My Drive/2024/FO local_EPS ICM/Diario/20250317_Trans2/FpUCD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B519E5DA-A9E8-46D4-B01D-A94BA62224EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{1B5DAEEE-67FF-644E-837F-5B0ABD560796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EDDCC0F-9847-4763-A416-B375A8F2E9B4}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{5CB7DE5F-F8DD-4C7C-901C-BE87FF788B57}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="23780" windowHeight="20500" xr2:uid="{5CB7DE5F-F8DD-4C7C-901C-BE87FF788B57}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="FpUCD-passenger" sheetId="2" r:id="rId3"/>
     <sheet name="FpUCD-freight" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30,6 +30,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="71">
   <si>
     <t>FpUCD Fares per Unit Cargo Distance</t>
   </si>
@@ -45,100 +47,49 @@
     <t>Source:</t>
   </si>
   <si>
-    <t>LDVs</t>
-  </si>
-  <si>
-    <t>HDVs</t>
-  </si>
-  <si>
-    <t>aircraft</t>
-  </si>
-  <si>
-    <t>rail</t>
-  </si>
-  <si>
-    <t>ships</t>
-  </si>
-  <si>
-    <t>motorbikes</t>
+    <t>General transportation costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinto poder article </t>
+  </si>
+  <si>
+    <t>https://quinto-poder.mx/tendencias/2022/3/16/semovi-2022-cuanto-cuesta-el-transporte-publico-en-cdmx-edomex-10608.html</t>
+  </si>
+  <si>
+    <t>Tren suburbano</t>
+  </si>
+  <si>
+    <t>http://fsuburbanos.com/secciones/operacion/costo_viaje.php</t>
+  </si>
+  <si>
+    <t>Aircraft</t>
+  </si>
+  <si>
+    <t>Instituto Mexicano del Transporte (SCT)</t>
+  </si>
+  <si>
+    <t>https://www.imt.mx/micrositios/integracion-del-transporte/monitor-del-estado-de-la-actividad-aerea-monitoreaa.html</t>
+  </si>
+  <si>
+    <t>https://www.imt.mx/archivos/publicaciones/PublicacionTecnica/pt608.pdf</t>
+  </si>
+  <si>
+    <t>collective bus data</t>
+  </si>
+  <si>
+    <t>Secretaria de movilidad - Estado de México</t>
+  </si>
+  <si>
+    <t>https://www.rastreator.mx/seguros-de-auto/articulos-destacados/tarifa-transporte-publico</t>
   </si>
   <si>
     <t>Notes</t>
   </si>
   <si>
-    <t>In the U.S. EPS, for passenger modes, a unit of "cargo distance" is a passenger-mile.</t>
-  </si>
-  <si>
-    <t>In the U.S. EPS, for freight modes, a unit of "cargo distance" is a freight ton-mile.</t>
-  </si>
-  <si>
-    <t>$/passenger*mile</t>
-  </si>
-  <si>
-    <t>$/ton*mile</t>
-  </si>
-  <si>
-    <t>(i.e. they rise at the rate of inflation).</t>
-  </si>
-  <si>
-    <t>We assume fares remain constant in the future after adjustment for inflation</t>
-  </si>
-  <si>
-    <t>General transportation costs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quinto poder article </t>
-  </si>
-  <si>
-    <t>https://quinto-poder.mx/tendencias/2022/3/16/semovi-2022-cuanto-cuesta-el-transporte-publico-en-cdmx-edomex-10608.html</t>
-  </si>
-  <si>
-    <t>Tren suburbano</t>
-  </si>
-  <si>
-    <t>http://fsuburbanos.com/secciones/operacion/costo_viaje.php</t>
-  </si>
-  <si>
-    <t>Aircraft</t>
-  </si>
-  <si>
-    <t>Instituto Mexicano del Transporte (SCT)</t>
-  </si>
-  <si>
-    <t>https://www.imt.mx/micrositios/integracion-del-transporte/monitor-del-estado-de-la-actividad-aerea-monitoreaa.html</t>
-  </si>
-  <si>
-    <t>https://www.imt.mx/archivos/publicaciones/PublicacionTecnica/pt608.pdf</t>
-  </si>
-  <si>
-    <t>collective bus data</t>
-  </si>
-  <si>
-    <t>Secretaria de movilidad - Estado de México</t>
-  </si>
-  <si>
-    <t>https://www.rastreator.mx/seguros-de-auto/articulos-destacados/tarifa-transporte-publico</t>
-  </si>
-  <si>
-    <t>ANÁLISIS DEL SISTEMA DE TRANSPORTE PÚBLICO DE NUEVO LEÓN</t>
-  </si>
-  <si>
-    <t>Asociación de transporte público de pasajeros de monterrey</t>
-  </si>
-  <si>
-    <t>http://www.hcnl.gob.mx/hacia_la_modernizacion_del_marco_normativo_en_materia_de_movilidad_y_transporte/pdf/06-ATPPNL.pdf</t>
-  </si>
-  <si>
-    <t>Slide 11, 23</t>
-  </si>
-  <si>
-    <t>Pasajero 7 noticias- LEÓN TIENE EL TRANSPORTE PÚBLICO POR VIAJE, MÁS ECONÓMICO DE ENTRE 15 DE LAS CIUDADES MÁS IMPORTANTES DEL PAÍS.</t>
-  </si>
-  <si>
-    <t>http://www.pasajero7.com/leon-transporte-publico-viaje-economico-15-las-ciudades-importantes-del-pais/</t>
-  </si>
-  <si>
-    <t>EDOMEX</t>
+    <t>For passenger modes, a unit of "cargo distance" is a passenger-mile.</t>
+  </si>
+  <si>
+    <t>For freight modes, a unit of "cargo distance" is a freight ton-mile.</t>
   </si>
   <si>
     <t>OTHER</t>
@@ -334,7 +285,13 @@
     <t>Zacatecas: $ 7.50 pesos.</t>
   </si>
   <si>
-    <t>2019 to 2012 USD</t>
+    <t>mxn/usd 2022</t>
+  </si>
+  <si>
+    <t>2022 to 2012 USD</t>
+  </si>
+  <si>
+    <t>km/miles</t>
   </si>
   <si>
     <t>FpUCD-passenger</t>
@@ -343,9 +300,6 @@
     <t>trip cost</t>
   </si>
   <si>
-    <t>2019 to 2012</t>
-  </si>
-  <si>
     <t>average trip</t>
   </si>
   <si>
@@ -361,7 +315,7 @@
     <t>mxn</t>
   </si>
   <si>
-    <t>2019 usd</t>
+    <t>2022 usd</t>
   </si>
   <si>
     <t>km</t>
@@ -370,13 +324,37 @@
     <t>miles</t>
   </si>
   <si>
+    <t>$/passenger*mile</t>
+  </si>
+  <si>
+    <t>LDVs</t>
+  </si>
+  <si>
     <t>colectivo</t>
   </si>
   <si>
+    <t>HDVs</t>
+  </si>
+  <si>
     <t>BRT</t>
   </si>
   <si>
+    <t>aircraft</t>
+  </si>
+  <si>
+    <t>rail</t>
+  </si>
+  <si>
     <t>metro</t>
+  </si>
+  <si>
+    <t>ships</t>
+  </si>
+  <si>
+    <t>motorbikes</t>
+  </si>
+  <si>
+    <t>$/ton*mile</t>
   </si>
 </sst>
 </file>
@@ -386,7 +364,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###0.00_)"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -463,6 +441,13 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -520,7 +505,7 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -544,6 +529,8 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="3" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="2" fontId="5" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Data" xfId="1" xr:uid="{4577C8A8-578A-43E3-8B00-19E95D726070}"/>
@@ -572,74 +559,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>327025</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>111126</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="Pasaje mínimo Edomex 2022">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6E17DB5-5F81-4FD0-B9AC-2EEF555F27CD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="733425" y="8220075"/>
-          <a:ext cx="9766300" cy="6778626"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>98</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>165100</xdr:colOff>
-      <xdr:row>121</xdr:row>
+      <xdr:row>112</xdr:row>
       <xdr:rowOff>24853</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -656,7 +582,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -683,13 +609,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>122</xdr:row>
+      <xdr:row>113</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>165100</xdr:colOff>
-      <xdr:row>159</xdr:row>
+      <xdr:row>150</xdr:row>
       <xdr:rowOff>112828</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -706,7 +632,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -725,6 +651,72 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>479425</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>9526</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Pasaje mínimo Edomex 2022">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EF187F4-FE0F-5344-927B-894F65D4F7EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="2476500"/>
+          <a:ext cx="10931525" cy="5915026"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -1029,8 +1021,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3168012A-7293-4AC1-A8AA-296A541E4584}">
-  <dimension ref="A1:D333"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:D324"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
     <col min="2" max="2" width="68.42578125" customWidth="1"/>
@@ -1046,13 +1038,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="4"/>
       <c r="B4" s="5" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1064,7 +1056,7 @@
     <row r="6" spans="1:2">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1074,7 +1066,7 @@
     <row r="8" spans="1:2">
       <c r="A8" s="4"/>
       <c r="B8" s="5" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1086,7 +1078,7 @@
     <row r="10" spans="1:2">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1096,13 +1088,13 @@
     <row r="12" spans="1:2">
       <c r="A12" s="4"/>
       <c r="B12" s="8" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="4"/>
       <c r="B13" s="8" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1114,13 +1106,13 @@
     <row r="15" spans="1:2">
       <c r="A15" s="4"/>
       <c r="B15" s="4" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="4"/>
       <c r="B16" s="4" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1130,13 +1122,13 @@
     <row r="18" spans="1:2">
       <c r="A18" s="4"/>
       <c r="B18" s="6" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="4"/>
       <c r="B19" s="4" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1148,13 +1140,13 @@
     <row r="21" spans="1:2">
       <c r="A21" s="4"/>
       <c r="B21" s="4" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="4"/>
       <c r="B22" s="9" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1163,33 +1155,29 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="4"/>
-      <c r="B24" t="s">
-        <v>27</v>
-      </c>
+      <c r="B24" s="4"/>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="4"/>
-      <c r="B25" s="7">
-        <v>2018</v>
-      </c>
+      <c r="B25" s="4"/>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4" t="s">
-        <v>28</v>
-      </c>
+      <c r="A26" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="4"/>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="4"/>
-      <c r="B27" s="9" t="s">
-        <v>29</v>
-      </c>
+      <c r="A27" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="4"/>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4" t="s">
-        <v>30</v>
-      </c>
+      <c r="A28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" s="4"/>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="4"/>
@@ -1197,477 +1185,422 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="4"/>
-      <c r="B30" s="4" t="s">
-        <v>31</v>
-      </c>
+      <c r="B30" s="4"/>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="4"/>
-      <c r="B31" s="7">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4" t="s">
+      <c r="B31" s="4"/>
+    </row>
+    <row r="33" spans="2:2" s="4" customFormat="1">
+      <c r="B33"/>
+    </row>
+    <row r="34" spans="2:2" s="4" customFormat="1" ht="12.95"/>
+    <row r="35" spans="2:2" s="4" customFormat="1" ht="12.95"/>
+    <row r="36" spans="2:2" s="4" customFormat="1" ht="12.95"/>
+    <row r="37" spans="2:2" s="4" customFormat="1" ht="12.95"/>
+    <row r="38" spans="2:2" s="4" customFormat="1" ht="12.95"/>
+    <row r="39" spans="2:2" s="4" customFormat="1" ht="12.95"/>
+    <row r="40" spans="2:2" s="4" customFormat="1" ht="12.95"/>
+    <row r="41" spans="2:2" s="4" customFormat="1" ht="12.95"/>
+    <row r="42" spans="2:2" s="4" customFormat="1" ht="12.95"/>
+    <row r="43" spans="2:2" s="4" customFormat="1" ht="12.95"/>
+    <row r="44" spans="2:2" s="4" customFormat="1" ht="12.95"/>
+    <row r="45" spans="2:2" s="4" customFormat="1" ht="12.95"/>
+    <row r="46" spans="2:2" s="4" customFormat="1" ht="12.95"/>
+    <row r="47" spans="2:2" s="4" customFormat="1" ht="12.95"/>
+    <row r="48" spans="2:2" s="4" customFormat="1" ht="12.95"/>
+    <row r="49" s="4" customFormat="1" ht="12.95"/>
+    <row r="50" s="4" customFormat="1" ht="12.95"/>
+    <row r="51" s="4" customFormat="1" ht="12.95"/>
+    <row r="52" s="4" customFormat="1" ht="12.95"/>
+    <row r="53" s="4" customFormat="1" ht="12.95"/>
+    <row r="54" s="4" customFormat="1" ht="12.95"/>
+    <row r="55" s="4" customFormat="1" ht="12.95"/>
+    <row r="56" s="4" customFormat="1" ht="12.95"/>
+    <row r="57" s="4" customFormat="1" ht="12.95"/>
+    <row r="58" s="4" customFormat="1" ht="12.95"/>
+    <row r="59" s="4" customFormat="1" ht="12.95"/>
+    <row r="60" s="4" customFormat="1" ht="12.95"/>
+    <row r="61" s="4" customFormat="1" ht="12.95"/>
+    <row r="62" s="4" customFormat="1" ht="12.95"/>
+    <row r="63" s="4" customFormat="1" ht="12.95"/>
+    <row r="64" s="4" customFormat="1" ht="12.95"/>
+    <row r="65" spans="1:4" s="4" customFormat="1" ht="12.95"/>
+    <row r="66" spans="1:4" s="4" customFormat="1" ht="12.95"/>
+    <row r="67" spans="1:4" s="4" customFormat="1" ht="12.95"/>
+    <row r="68" spans="1:4" s="4" customFormat="1" ht="12.95"/>
+    <row r="69" spans="1:4" s="4" customFormat="1" ht="12.95"/>
+    <row r="70" spans="1:4" s="4" customFormat="1" ht="18">
+      <c r="A70" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" s="4" customFormat="1">
+      <c r="B71"/>
+      <c r="D71"/>
+    </row>
+    <row r="72" spans="1:4" s="4" customFormat="1" ht="20.100000000000001">
+      <c r="B72" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D72" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" s="4" customFormat="1" ht="20.100000000000001">
+      <c r="B73" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" s="4" customFormat="1" ht="20.100000000000001">
+      <c r="B74" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" s="4" customFormat="1" ht="20.100000000000001">
+      <c r="B75" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" s="4" customFormat="1" ht="20.100000000000001">
+      <c r="B76" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" s="4" customFormat="1" ht="20.100000000000001">
+      <c r="B77" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D77"/>
+    </row>
+    <row r="78" spans="1:4" s="4" customFormat="1" ht="20.100000000000001">
+      <c r="B78" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D78" s="13" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B35" s="4"/>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B36" s="4"/>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B37" s="4"/>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B39" s="4"/>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B40" s="4"/>
-    </row>
-    <row r="42" spans="1:2" s="4" customFormat="1" ht="15.75">
-      <c r="A42" s="4" t="s">
+    <row r="79" spans="1:4" s="4" customFormat="1" ht="20.100000000000001">
+      <c r="B79" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B42"/>
-    </row>
-    <row r="43" spans="1:2" s="4" customFormat="1" ht="12.75"/>
-    <row r="44" spans="1:2" s="4" customFormat="1" ht="12.75"/>
-    <row r="45" spans="1:2" s="4" customFormat="1" ht="12.75"/>
-    <row r="46" spans="1:2" s="4" customFormat="1" ht="12.75"/>
-    <row r="47" spans="1:2" s="4" customFormat="1" ht="12.75"/>
-    <row r="48" spans="1:2" s="4" customFormat="1" ht="12.75"/>
-    <row r="49" s="4" customFormat="1" ht="12.75"/>
-    <row r="50" s="4" customFormat="1" ht="12.75"/>
-    <row r="51" s="4" customFormat="1" ht="12.75"/>
-    <row r="52" s="4" customFormat="1" ht="12.75"/>
-    <row r="53" s="4" customFormat="1" ht="12.75"/>
-    <row r="54" s="4" customFormat="1" ht="12.75"/>
-    <row r="55" s="4" customFormat="1" ht="12.75"/>
-    <row r="56" s="4" customFormat="1" ht="12.75"/>
-    <row r="57" s="4" customFormat="1" ht="12.75"/>
-    <row r="58" s="4" customFormat="1" ht="12.75"/>
-    <row r="59" s="4" customFormat="1" ht="12.75"/>
-    <row r="60" s="4" customFormat="1" ht="12.75"/>
-    <row r="61" s="4" customFormat="1" ht="12.75"/>
-    <row r="62" s="4" customFormat="1" ht="12.75"/>
-    <row r="63" s="4" customFormat="1" ht="12.75"/>
-    <row r="64" s="4" customFormat="1" ht="12.75"/>
-    <row r="65" spans="1:4" s="4" customFormat="1" ht="12.75"/>
-    <row r="66" spans="1:4" s="4" customFormat="1" ht="12.75"/>
-    <row r="67" spans="1:4" s="4" customFormat="1" ht="12.75"/>
-    <row r="68" spans="1:4" s="4" customFormat="1" ht="12.75"/>
-    <row r="69" spans="1:4" s="4" customFormat="1" ht="12.75"/>
-    <row r="70" spans="1:4" s="4" customFormat="1" ht="12.75"/>
-    <row r="71" spans="1:4" s="4" customFormat="1" ht="12.75"/>
-    <row r="72" spans="1:4" s="4" customFormat="1" ht="12.75"/>
-    <row r="73" spans="1:4" s="4" customFormat="1" ht="12.75"/>
-    <row r="74" spans="1:4" s="4" customFormat="1" ht="12.75"/>
-    <row r="75" spans="1:4" s="4" customFormat="1" ht="12.75"/>
-    <row r="76" spans="1:4" s="4" customFormat="1" ht="12.75"/>
-    <row r="77" spans="1:4" s="4" customFormat="1" ht="12.75"/>
-    <row r="78" spans="1:4" s="4" customFormat="1" ht="12.75"/>
-    <row r="79" spans="1:4" s="4" customFormat="1" ht="17.25">
-      <c r="A79" s="4" t="s">
+      <c r="D79" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B79" s="10" t="s">
+    </row>
+    <row r="80" spans="1:4" s="4" customFormat="1" ht="20.100000000000001">
+      <c r="B80" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C79" s="4" t="s">
+    </row>
+    <row r="81" spans="2:4" s="4" customFormat="1" ht="20.100000000000001">
+      <c r="B81" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D79" s="11" t="s">
+      <c r="C81" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" s="4" customFormat="1" ht="15.75">
-      <c r="B80"/>
-      <c r="D80"/>
-    </row>
-    <row r="81" spans="2:4" s="4" customFormat="1" ht="20.25">
-      <c r="B81" s="12" t="s">
+      <c r="D81" s="11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4" s="4" customFormat="1" ht="20.100000000000001">
+      <c r="B82" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D81" s="13" t="s">
+      <c r="D82" s="14" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="82" spans="2:4" s="4" customFormat="1" ht="20.25">
-      <c r="B82" s="12" t="s">
+    <row r="83" spans="2:4" s="4" customFormat="1" ht="20.100000000000001">
+      <c r="B83" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D82" s="13" t="s">
+      <c r="D83" s="14" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="83" spans="2:4" s="4" customFormat="1" ht="20.25">
-      <c r="B83" s="12" t="s">
+    <row r="84" spans="2:4" s="4" customFormat="1" ht="20.100000000000001">
+      <c r="B84" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="D83" s="13" t="s">
+      <c r="D84" s="14" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="84" spans="2:4" s="4" customFormat="1" ht="20.25">
-      <c r="B84" s="12" t="s">
+    <row r="85" spans="2:4" s="4" customFormat="1" ht="20.100000000000001">
+      <c r="B85" s="12" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="85" spans="2:4" s="4" customFormat="1" ht="20.25">
-      <c r="B85" s="12" t="s">
+    <row r="86" spans="2:4" s="4" customFormat="1" ht="20.100000000000001">
+      <c r="B86" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D85" s="11" t="s">
+    </row>
+    <row r="87" spans="2:4" s="4" customFormat="1" ht="20.100000000000001">
+      <c r="B87" s="12" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="86" spans="2:4" s="4" customFormat="1" ht="20.25">
-      <c r="B86" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D86"/>
-    </row>
-    <row r="87" spans="2:4" s="4" customFormat="1" ht="20.25">
-      <c r="B87" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D87" s="13" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="88" spans="2:4" s="4" customFormat="1" ht="20.25">
-      <c r="B88" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="89" spans="2:4" s="4" customFormat="1" ht="20.25">
-      <c r="B89" s="12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="90" spans="2:4" s="4" customFormat="1" ht="20.25">
-      <c r="B90" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D90" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="91" spans="2:4" s="4" customFormat="1" ht="20.25">
-      <c r="B91" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="D91" s="14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="92" spans="2:4" s="4" customFormat="1" ht="20.25">
-      <c r="B92" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D92" s="14" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="93" spans="2:4" s="4" customFormat="1" ht="20.25">
-      <c r="B93" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="D93" s="14" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="94" spans="2:4" s="4" customFormat="1" ht="20.25">
-      <c r="B94" s="12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="95" spans="2:4" s="4" customFormat="1" ht="20.25">
-      <c r="B95" s="12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="96" spans="2:4" s="4" customFormat="1" ht="20.25">
-      <c r="B96" s="12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="97" spans="4:4" s="4" customFormat="1" ht="12.75"/>
-    <row r="98" spans="4:4" s="4" customFormat="1" ht="12.75"/>
-    <row r="99" spans="4:4" s="4" customFormat="1" ht="12.75"/>
-    <row r="100" spans="4:4" s="4" customFormat="1" ht="12.75"/>
-    <row r="101" spans="4:4" s="4" customFormat="1" ht="15.75">
-      <c r="D101"/>
-    </row>
-    <row r="102" spans="4:4" s="4" customFormat="1" ht="12.75"/>
-    <row r="103" spans="4:4" s="4" customFormat="1" ht="12.75"/>
-    <row r="104" spans="4:4" s="4" customFormat="1" ht="12.75"/>
-    <row r="105" spans="4:4" s="4" customFormat="1" ht="12.75"/>
-    <row r="106" spans="4:4" s="4" customFormat="1" ht="12.75"/>
-    <row r="107" spans="4:4" s="4" customFormat="1" ht="12.75"/>
-    <row r="108" spans="4:4" s="4" customFormat="1" ht="12.75"/>
-    <row r="109" spans="4:4" s="4" customFormat="1" ht="12.75"/>
-    <row r="110" spans="4:4" s="4" customFormat="1" ht="12.75"/>
-    <row r="111" spans="4:4" s="4" customFormat="1" ht="12.75"/>
-    <row r="112" spans="4:4" s="4" customFormat="1" ht="12.75"/>
-    <row r="113" s="4" customFormat="1" ht="12.75"/>
-    <row r="114" s="4" customFormat="1" ht="12.75"/>
-    <row r="115" s="4" customFormat="1" ht="12.75"/>
-    <row r="116" s="4" customFormat="1" ht="12.75"/>
-    <row r="117" s="4" customFormat="1" ht="12.75"/>
-    <row r="118" s="4" customFormat="1" ht="12.75"/>
-    <row r="119" s="4" customFormat="1" ht="12.75"/>
-    <row r="120" s="4" customFormat="1" ht="12.75"/>
-    <row r="121" s="4" customFormat="1" ht="12.75"/>
-    <row r="122" s="4" customFormat="1" ht="12.75"/>
-    <row r="123" s="4" customFormat="1" ht="12.75"/>
-    <row r="124" s="4" customFormat="1" ht="12.75"/>
-    <row r="125" s="4" customFormat="1" ht="12.75"/>
-    <row r="126" s="4" customFormat="1" ht="12.75"/>
-    <row r="127" s="4" customFormat="1" ht="12.75"/>
-    <row r="128" s="4" customFormat="1" ht="12.75"/>
-    <row r="129" s="4" customFormat="1" ht="12.75"/>
-    <row r="130" s="4" customFormat="1" ht="12.75"/>
-    <row r="131" s="4" customFormat="1" ht="12.75"/>
-    <row r="132" s="4" customFormat="1" ht="12.75"/>
-    <row r="133" s="4" customFormat="1" ht="12.75"/>
-    <row r="134" s="4" customFormat="1" ht="12.75"/>
-    <row r="135" s="4" customFormat="1" ht="12.75"/>
-    <row r="136" s="4" customFormat="1" ht="12.75"/>
-    <row r="137" s="4" customFormat="1" ht="12.75"/>
-    <row r="138" s="4" customFormat="1" ht="12.75"/>
-    <row r="139" s="4" customFormat="1" ht="12.75"/>
-    <row r="140" s="4" customFormat="1" ht="12.75"/>
-    <row r="141" s="4" customFormat="1" ht="12.75"/>
-    <row r="142" s="4" customFormat="1" ht="12.75"/>
-    <row r="143" s="4" customFormat="1" ht="12.75"/>
-    <row r="144" s="4" customFormat="1" ht="12.75"/>
-    <row r="145" s="4" customFormat="1" ht="12.75"/>
-    <row r="146" s="4" customFormat="1" ht="12.75"/>
-    <row r="147" s="4" customFormat="1" ht="12.75"/>
-    <row r="148" s="4" customFormat="1" ht="12.75"/>
-    <row r="149" s="4" customFormat="1" ht="12.75"/>
-    <row r="150" s="4" customFormat="1" ht="12.75"/>
-    <row r="151" s="4" customFormat="1" ht="12.75"/>
-    <row r="152" s="4" customFormat="1" ht="12.75"/>
-    <row r="153" s="4" customFormat="1" ht="12.75"/>
-    <row r="154" s="4" customFormat="1" ht="12.75"/>
-    <row r="155" s="4" customFormat="1" ht="12.75"/>
-    <row r="156" s="4" customFormat="1" ht="12.75"/>
-    <row r="157" s="4" customFormat="1" ht="12.75"/>
-    <row r="158" s="4" customFormat="1" ht="12.75"/>
-    <row r="159" s="4" customFormat="1" ht="12.75"/>
-    <row r="160" s="4" customFormat="1" ht="12.75"/>
-    <row r="161" s="4" customFormat="1" ht="12.75"/>
-    <row r="162" s="4" customFormat="1" ht="12.75"/>
-    <row r="163" s="4" customFormat="1" ht="12.75"/>
-    <row r="164" s="4" customFormat="1" ht="12.75"/>
-    <row r="165" s="4" customFormat="1" ht="12.75"/>
-    <row r="166" s="4" customFormat="1" ht="12.75"/>
-    <row r="167" s="4" customFormat="1" ht="12.75"/>
-    <row r="168" s="4" customFormat="1" ht="12.75"/>
-    <row r="169" s="4" customFormat="1" ht="12.75"/>
-    <row r="170" s="4" customFormat="1" ht="12.75"/>
-    <row r="171" s="4" customFormat="1" ht="12.75"/>
-    <row r="172" s="4" customFormat="1" ht="12.75"/>
-    <row r="173" s="4" customFormat="1" ht="12.75"/>
-    <row r="174" s="4" customFormat="1" ht="12.75"/>
-    <row r="175" s="4" customFormat="1" ht="12.75"/>
-    <row r="176" s="4" customFormat="1" ht="12.75"/>
-    <row r="177" s="4" customFormat="1" ht="12.75"/>
-    <row r="178" s="4" customFormat="1" ht="12.75"/>
-    <row r="179" s="4" customFormat="1" ht="12.75"/>
-    <row r="180" s="4" customFormat="1" ht="12.75"/>
-    <row r="181" s="4" customFormat="1" ht="12.75"/>
-    <row r="182" s="4" customFormat="1" ht="12.75"/>
-    <row r="183" s="4" customFormat="1" ht="12.75"/>
-    <row r="184" s="4" customFormat="1" ht="12.75"/>
-    <row r="185" s="4" customFormat="1" ht="12.75"/>
-    <row r="186" s="4" customFormat="1" ht="12.75"/>
-    <row r="187" s="4" customFormat="1" ht="12.75"/>
-    <row r="188" s="4" customFormat="1" ht="12.75"/>
-    <row r="189" s="4" customFormat="1" ht="12.75"/>
-    <row r="190" s="4" customFormat="1" ht="12.75"/>
-    <row r="191" s="4" customFormat="1" ht="12.75"/>
-    <row r="192" s="4" customFormat="1" ht="12.75"/>
-    <row r="193" s="4" customFormat="1" ht="12.75"/>
-    <row r="194" s="4" customFormat="1" ht="12.75"/>
-    <row r="195" s="4" customFormat="1" ht="12.75"/>
-    <row r="196" s="4" customFormat="1" ht="12.75"/>
-    <row r="197" s="4" customFormat="1" ht="12.75"/>
-    <row r="198" s="4" customFormat="1" ht="12.75"/>
-    <row r="199" s="4" customFormat="1" ht="12.75"/>
-    <row r="200" s="4" customFormat="1" ht="12.75"/>
-    <row r="201" s="4" customFormat="1" ht="12.75"/>
-    <row r="202" s="4" customFormat="1" ht="12.75"/>
-    <row r="203" s="4" customFormat="1" ht="12.75"/>
-    <row r="204" s="4" customFormat="1" ht="12.75"/>
-    <row r="205" s="4" customFormat="1" ht="12.75"/>
-    <row r="206" s="4" customFormat="1" ht="12.75"/>
-    <row r="207" s="4" customFormat="1" ht="12.75"/>
-    <row r="208" s="4" customFormat="1" ht="12.75"/>
-    <row r="209" s="4" customFormat="1" ht="12.75"/>
-    <row r="210" s="4" customFormat="1" ht="12.75"/>
-    <row r="211" s="4" customFormat="1" ht="12.75"/>
-    <row r="212" s="4" customFormat="1" ht="12.75"/>
-    <row r="213" s="4" customFormat="1" ht="12.75"/>
-    <row r="214" s="4" customFormat="1" ht="12.75"/>
-    <row r="215" s="4" customFormat="1" ht="12.75"/>
-    <row r="216" s="4" customFormat="1" ht="12.75"/>
-    <row r="217" s="4" customFormat="1" ht="12.75"/>
-    <row r="218" s="4" customFormat="1" ht="12.75"/>
-    <row r="219" s="4" customFormat="1" ht="12.75"/>
-    <row r="220" s="4" customFormat="1" ht="12.75"/>
-    <row r="221" s="4" customFormat="1" ht="12.75"/>
-    <row r="222" s="4" customFormat="1" ht="12.75"/>
-    <row r="223" s="4" customFormat="1" ht="12.75"/>
-    <row r="224" s="4" customFormat="1" ht="12.75"/>
-    <row r="225" s="4" customFormat="1" ht="12.75"/>
-    <row r="226" s="4" customFormat="1" ht="12.75"/>
-    <row r="227" s="4" customFormat="1" ht="12.75"/>
-    <row r="228" s="4" customFormat="1" ht="12.75"/>
-    <row r="229" s="4" customFormat="1" ht="12.75"/>
-    <row r="230" s="4" customFormat="1" ht="12.75"/>
-    <row r="231" s="4" customFormat="1" ht="12.75"/>
-    <row r="232" s="4" customFormat="1" ht="12.75"/>
-    <row r="233" s="4" customFormat="1" ht="12.75"/>
-    <row r="234" s="4" customFormat="1" ht="12.75"/>
-    <row r="235" s="4" customFormat="1" ht="12.75"/>
-    <row r="236" s="4" customFormat="1" ht="12.75"/>
-    <row r="237" s="4" customFormat="1" ht="12.75"/>
-    <row r="238" s="4" customFormat="1" ht="12.75"/>
-    <row r="239" s="4" customFormat="1" ht="12.75"/>
-    <row r="240" s="4" customFormat="1" ht="12.75"/>
-    <row r="241" s="4" customFormat="1" ht="12.75"/>
-    <row r="242" s="4" customFormat="1" ht="12.75"/>
-    <row r="243" s="4" customFormat="1" ht="12.75"/>
-    <row r="244" s="4" customFormat="1" ht="12.75"/>
-    <row r="245" s="4" customFormat="1" ht="12.75"/>
-    <row r="246" s="4" customFormat="1" ht="12.75"/>
-    <row r="247" s="4" customFormat="1" ht="12.75"/>
-    <row r="248" s="4" customFormat="1" ht="12.75"/>
-    <row r="249" s="4" customFormat="1" ht="12.75"/>
-    <row r="250" s="4" customFormat="1" ht="12.75"/>
-    <row r="251" s="4" customFormat="1" ht="12.75"/>
-    <row r="252" s="4" customFormat="1" ht="12.75"/>
-    <row r="253" s="4" customFormat="1" ht="12.75"/>
-    <row r="254" s="4" customFormat="1" ht="12.75"/>
-    <row r="255" s="4" customFormat="1" ht="12.75"/>
-    <row r="256" s="4" customFormat="1" ht="12.75"/>
-    <row r="257" s="4" customFormat="1" ht="12.75"/>
-    <row r="258" s="4" customFormat="1" ht="12.75"/>
-    <row r="259" s="4" customFormat="1" ht="12.75"/>
-    <row r="260" s="4" customFormat="1" ht="12.75"/>
-    <row r="261" s="4" customFormat="1" ht="12.75"/>
-    <row r="262" s="4" customFormat="1" ht="12.75"/>
-    <row r="263" s="4" customFormat="1" ht="12.75"/>
-    <row r="264" s="4" customFormat="1" ht="12.75"/>
-    <row r="265" s="4" customFormat="1" ht="12.75"/>
-    <row r="266" s="4" customFormat="1" ht="12.75"/>
-    <row r="267" s="4" customFormat="1" ht="12.75"/>
-    <row r="268" s="4" customFormat="1" ht="12.75"/>
-    <row r="269" s="4" customFormat="1" ht="12.75"/>
-    <row r="270" s="4" customFormat="1" ht="12.75"/>
-    <row r="271" s="4" customFormat="1" ht="12.75"/>
-    <row r="272" s="4" customFormat="1" ht="12.75"/>
-    <row r="273" s="4" customFormat="1" ht="12.75"/>
-    <row r="274" s="4" customFormat="1" ht="12.75"/>
-    <row r="275" s="4" customFormat="1" ht="12.75"/>
-    <row r="276" s="4" customFormat="1" ht="12.75"/>
-    <row r="277" s="4" customFormat="1" ht="12.75"/>
-    <row r="278" s="4" customFormat="1" ht="12.75"/>
-    <row r="279" s="4" customFormat="1" ht="12.75"/>
-    <row r="280" s="4" customFormat="1" ht="12.75"/>
-    <row r="281" s="4" customFormat="1" ht="12.75"/>
-    <row r="282" s="4" customFormat="1" ht="12.75"/>
-    <row r="283" s="4" customFormat="1" ht="12.75"/>
-    <row r="284" s="4" customFormat="1" ht="12.75"/>
-    <row r="285" s="4" customFormat="1" ht="12.75"/>
-    <row r="286" s="4" customFormat="1" ht="12.75"/>
-    <row r="287" s="4" customFormat="1" ht="12.75"/>
-    <row r="288" s="4" customFormat="1" ht="12.75"/>
-    <row r="289" s="4" customFormat="1" ht="12.75"/>
-    <row r="290" s="4" customFormat="1" ht="12.75"/>
-    <row r="291" s="4" customFormat="1" ht="12.75"/>
-    <row r="292" s="4" customFormat="1" ht="12.75"/>
-    <row r="293" s="4" customFormat="1" ht="12.75"/>
-    <row r="294" s="4" customFormat="1" ht="12.75"/>
-    <row r="295" s="4" customFormat="1" ht="12.75"/>
-    <row r="296" s="4" customFormat="1" ht="12.75"/>
-    <row r="297" s="4" customFormat="1" ht="12.75"/>
-    <row r="298" s="4" customFormat="1" ht="12.75"/>
-    <row r="299" s="4" customFormat="1" ht="12.75"/>
-    <row r="300" s="4" customFormat="1" ht="12.75"/>
-    <row r="301" s="4" customFormat="1" ht="12.75"/>
-    <row r="302" s="4" customFormat="1" ht="12.75"/>
-    <row r="303" s="4" customFormat="1" ht="12.75"/>
-    <row r="304" s="4" customFormat="1" ht="12.75"/>
-    <row r="305" s="4" customFormat="1" ht="12.75"/>
-    <row r="306" s="4" customFormat="1" ht="12.75"/>
-    <row r="307" s="4" customFormat="1" ht="12.75"/>
-    <row r="308" s="4" customFormat="1" ht="12.75"/>
-    <row r="309" s="4" customFormat="1" ht="12.75"/>
-    <row r="310" s="4" customFormat="1" ht="12.75"/>
-    <row r="311" s="4" customFormat="1" ht="12.75"/>
-    <row r="312" s="4" customFormat="1" ht="12.75"/>
-    <row r="313" s="4" customFormat="1" ht="12.75"/>
-    <row r="314" s="4" customFormat="1" ht="12.75"/>
-    <row r="315" s="4" customFormat="1" ht="12.75"/>
-    <row r="316" s="4" customFormat="1" ht="12.75"/>
-    <row r="317" s="4" customFormat="1" ht="12.75"/>
-    <row r="318" s="4" customFormat="1" ht="12.75"/>
-    <row r="319" s="4" customFormat="1" ht="12.75"/>
-    <row r="320" s="4" customFormat="1" ht="12.75"/>
-    <row r="321" s="4" customFormat="1" ht="12.75"/>
-    <row r="322" s="4" customFormat="1" ht="12.75"/>
-    <row r="323" s="4" customFormat="1" ht="12.75"/>
-    <row r="324" s="4" customFormat="1" ht="12.75"/>
-    <row r="325" s="4" customFormat="1" ht="12.75"/>
-    <row r="326" s="4" customFormat="1" ht="12.75"/>
-    <row r="327" s="4" customFormat="1" ht="12.75"/>
-    <row r="328" s="4" customFormat="1" ht="12.75"/>
-    <row r="329" s="4" customFormat="1" ht="12.75"/>
-    <row r="330" s="4" customFormat="1" ht="12.75"/>
-    <row r="331" s="4" customFormat="1" ht="12.75"/>
-    <row r="332" s="4" customFormat="1" ht="12.75"/>
-    <row r="333" s="4" customFormat="1" ht="12.75"/>
+    <row r="88" spans="2:4" s="4" customFormat="1" ht="12.95"/>
+    <row r="89" spans="2:4" s="4" customFormat="1" ht="12.95"/>
+    <row r="90" spans="2:4" s="4" customFormat="1" ht="12.95"/>
+    <row r="91" spans="2:4" s="4" customFormat="1" ht="12.95"/>
+    <row r="92" spans="2:4" s="4" customFormat="1">
+      <c r="D92"/>
+    </row>
+    <row r="93" spans="2:4" s="4" customFormat="1" ht="12.95"/>
+    <row r="94" spans="2:4" s="4" customFormat="1" ht="12.95"/>
+    <row r="95" spans="2:4" s="4" customFormat="1" ht="12.95"/>
+    <row r="96" spans="2:4" s="4" customFormat="1" ht="12.95"/>
+    <row r="97" s="4" customFormat="1" ht="12.95"/>
+    <row r="98" s="4" customFormat="1" ht="12.95"/>
+    <row r="99" s="4" customFormat="1" ht="12.95"/>
+    <row r="100" s="4" customFormat="1" ht="12.95"/>
+    <row r="101" s="4" customFormat="1" ht="12.95"/>
+    <row r="102" s="4" customFormat="1" ht="12.95"/>
+    <row r="103" s="4" customFormat="1" ht="12.95"/>
+    <row r="104" s="4" customFormat="1" ht="12.95"/>
+    <row r="105" s="4" customFormat="1" ht="12.95"/>
+    <row r="106" s="4" customFormat="1" ht="12.95"/>
+    <row r="107" s="4" customFormat="1" ht="12.95"/>
+    <row r="108" s="4" customFormat="1" ht="12.95"/>
+    <row r="109" s="4" customFormat="1" ht="12.95"/>
+    <row r="110" s="4" customFormat="1" ht="12.95"/>
+    <row r="111" s="4" customFormat="1" ht="12.95"/>
+    <row r="112" s="4" customFormat="1" ht="12.95"/>
+    <row r="113" s="4" customFormat="1" ht="12.95"/>
+    <row r="114" s="4" customFormat="1" ht="12.95"/>
+    <row r="115" s="4" customFormat="1" ht="12.95"/>
+    <row r="116" s="4" customFormat="1" ht="12.95"/>
+    <row r="117" s="4" customFormat="1" ht="12.95"/>
+    <row r="118" s="4" customFormat="1" ht="12.95"/>
+    <row r="119" s="4" customFormat="1" ht="12.95"/>
+    <row r="120" s="4" customFormat="1" ht="12.95"/>
+    <row r="121" s="4" customFormat="1" ht="12.95"/>
+    <row r="122" s="4" customFormat="1" ht="12.95"/>
+    <row r="123" s="4" customFormat="1" ht="12.95"/>
+    <row r="124" s="4" customFormat="1" ht="12.95"/>
+    <row r="125" s="4" customFormat="1" ht="12.95"/>
+    <row r="126" s="4" customFormat="1" ht="12.95"/>
+    <row r="127" s="4" customFormat="1" ht="12.95"/>
+    <row r="128" s="4" customFormat="1" ht="12.95"/>
+    <row r="129" s="4" customFormat="1" ht="12.95"/>
+    <row r="130" s="4" customFormat="1" ht="12.95"/>
+    <row r="131" s="4" customFormat="1" ht="12.95"/>
+    <row r="132" s="4" customFormat="1" ht="12.95"/>
+    <row r="133" s="4" customFormat="1" ht="12.95"/>
+    <row r="134" s="4" customFormat="1" ht="12.95"/>
+    <row r="135" s="4" customFormat="1" ht="12.95"/>
+    <row r="136" s="4" customFormat="1" ht="12.95"/>
+    <row r="137" s="4" customFormat="1" ht="12.95"/>
+    <row r="138" s="4" customFormat="1" ht="12.95"/>
+    <row r="139" s="4" customFormat="1" ht="12.95"/>
+    <row r="140" s="4" customFormat="1" ht="12.95"/>
+    <row r="141" s="4" customFormat="1" ht="12.95"/>
+    <row r="142" s="4" customFormat="1" ht="12.95"/>
+    <row r="143" s="4" customFormat="1" ht="12.95"/>
+    <row r="144" s="4" customFormat="1" ht="12.95"/>
+    <row r="145" s="4" customFormat="1" ht="12.95"/>
+    <row r="146" s="4" customFormat="1" ht="12.95"/>
+    <row r="147" s="4" customFormat="1" ht="12.95"/>
+    <row r="148" s="4" customFormat="1" ht="12.95"/>
+    <row r="149" s="4" customFormat="1" ht="12.95"/>
+    <row r="150" s="4" customFormat="1" ht="12.95"/>
+    <row r="151" s="4" customFormat="1" ht="12.95"/>
+    <row r="152" s="4" customFormat="1" ht="12.95"/>
+    <row r="153" s="4" customFormat="1" ht="12.95"/>
+    <row r="154" s="4" customFormat="1" ht="12.95"/>
+    <row r="155" s="4" customFormat="1" ht="12.95"/>
+    <row r="156" s="4" customFormat="1" ht="12.95"/>
+    <row r="157" s="4" customFormat="1" ht="12.95"/>
+    <row r="158" s="4" customFormat="1" ht="12.95"/>
+    <row r="159" s="4" customFormat="1" ht="12.95"/>
+    <row r="160" s="4" customFormat="1" ht="12.95"/>
+    <row r="161" s="4" customFormat="1" ht="12.95"/>
+    <row r="162" s="4" customFormat="1" ht="12.95"/>
+    <row r="163" s="4" customFormat="1" ht="12.95"/>
+    <row r="164" s="4" customFormat="1" ht="12.95"/>
+    <row r="165" s="4" customFormat="1" ht="12.95"/>
+    <row r="166" s="4" customFormat="1" ht="12.95"/>
+    <row r="167" s="4" customFormat="1" ht="12.95"/>
+    <row r="168" s="4" customFormat="1" ht="12.95"/>
+    <row r="169" s="4" customFormat="1" ht="12.95"/>
+    <row r="170" s="4" customFormat="1" ht="12.95"/>
+    <row r="171" s="4" customFormat="1" ht="12.95"/>
+    <row r="172" s="4" customFormat="1" ht="12.95"/>
+    <row r="173" s="4" customFormat="1" ht="12.95"/>
+    <row r="174" s="4" customFormat="1" ht="12.95"/>
+    <row r="175" s="4" customFormat="1" ht="12.95"/>
+    <row r="176" s="4" customFormat="1" ht="12.95"/>
+    <row r="177" s="4" customFormat="1" ht="12.95"/>
+    <row r="178" s="4" customFormat="1" ht="12.95"/>
+    <row r="179" s="4" customFormat="1" ht="12.95"/>
+    <row r="180" s="4" customFormat="1" ht="12.95"/>
+    <row r="181" s="4" customFormat="1" ht="12.95"/>
+    <row r="182" s="4" customFormat="1" ht="12.95"/>
+    <row r="183" s="4" customFormat="1" ht="12.95"/>
+    <row r="184" s="4" customFormat="1" ht="12.95"/>
+    <row r="185" s="4" customFormat="1" ht="12.95"/>
+    <row r="186" s="4" customFormat="1" ht="12.95"/>
+    <row r="187" s="4" customFormat="1" ht="12.95"/>
+    <row r="188" s="4" customFormat="1" ht="12.95"/>
+    <row r="189" s="4" customFormat="1" ht="12.95"/>
+    <row r="190" s="4" customFormat="1" ht="12.95"/>
+    <row r="191" s="4" customFormat="1" ht="12.95"/>
+    <row r="192" s="4" customFormat="1" ht="12.95"/>
+    <row r="193" s="4" customFormat="1" ht="12.95"/>
+    <row r="194" s="4" customFormat="1" ht="12.95"/>
+    <row r="195" s="4" customFormat="1" ht="12.95"/>
+    <row r="196" s="4" customFormat="1" ht="12.95"/>
+    <row r="197" s="4" customFormat="1" ht="12.95"/>
+    <row r="198" s="4" customFormat="1" ht="12.95"/>
+    <row r="199" s="4" customFormat="1" ht="12.95"/>
+    <row r="200" s="4" customFormat="1" ht="12.95"/>
+    <row r="201" s="4" customFormat="1" ht="12.95"/>
+    <row r="202" s="4" customFormat="1" ht="12.95"/>
+    <row r="203" s="4" customFormat="1" ht="12.95"/>
+    <row r="204" s="4" customFormat="1" ht="12.95"/>
+    <row r="205" s="4" customFormat="1" ht="12.95"/>
+    <row r="206" s="4" customFormat="1" ht="12.95"/>
+    <row r="207" s="4" customFormat="1" ht="12.95"/>
+    <row r="208" s="4" customFormat="1" ht="12.95"/>
+    <row r="209" s="4" customFormat="1" ht="12.95"/>
+    <row r="210" s="4" customFormat="1" ht="12.95"/>
+    <row r="211" s="4" customFormat="1" ht="12.95"/>
+    <row r="212" s="4" customFormat="1" ht="12.95"/>
+    <row r="213" s="4" customFormat="1" ht="12.95"/>
+    <row r="214" s="4" customFormat="1" ht="12.95"/>
+    <row r="215" s="4" customFormat="1" ht="12.95"/>
+    <row r="216" s="4" customFormat="1" ht="12.95"/>
+    <row r="217" s="4" customFormat="1" ht="12.95"/>
+    <row r="218" s="4" customFormat="1" ht="12.95"/>
+    <row r="219" s="4" customFormat="1" ht="12.95"/>
+    <row r="220" s="4" customFormat="1" ht="12.95"/>
+    <row r="221" s="4" customFormat="1" ht="12.95"/>
+    <row r="222" s="4" customFormat="1" ht="12.95"/>
+    <row r="223" s="4" customFormat="1" ht="12.95"/>
+    <row r="224" s="4" customFormat="1" ht="12.95"/>
+    <row r="225" s="4" customFormat="1" ht="12.95"/>
+    <row r="226" s="4" customFormat="1" ht="12.95"/>
+    <row r="227" s="4" customFormat="1" ht="12.95"/>
+    <row r="228" s="4" customFormat="1" ht="12.95"/>
+    <row r="229" s="4" customFormat="1" ht="12.95"/>
+    <row r="230" s="4" customFormat="1" ht="12.95"/>
+    <row r="231" s="4" customFormat="1" ht="12.95"/>
+    <row r="232" s="4" customFormat="1" ht="12.95"/>
+    <row r="233" s="4" customFormat="1" ht="12.95"/>
+    <row r="234" s="4" customFormat="1" ht="12.95"/>
+    <row r="235" s="4" customFormat="1" ht="12.95"/>
+    <row r="236" s="4" customFormat="1" ht="12.95"/>
+    <row r="237" s="4" customFormat="1" ht="12.95"/>
+    <row r="238" s="4" customFormat="1" ht="12.95"/>
+    <row r="239" s="4" customFormat="1" ht="12.95"/>
+    <row r="240" s="4" customFormat="1" ht="12.95"/>
+    <row r="241" s="4" customFormat="1" ht="12.95"/>
+    <row r="242" s="4" customFormat="1" ht="12.95"/>
+    <row r="243" s="4" customFormat="1" ht="12.95"/>
+    <row r="244" s="4" customFormat="1" ht="12.95"/>
+    <row r="245" s="4" customFormat="1" ht="12.95"/>
+    <row r="246" s="4" customFormat="1" ht="12.95"/>
+    <row r="247" s="4" customFormat="1" ht="12.95"/>
+    <row r="248" s="4" customFormat="1" ht="12.95"/>
+    <row r="249" s="4" customFormat="1" ht="12.95"/>
+    <row r="250" s="4" customFormat="1" ht="12.95"/>
+    <row r="251" s="4" customFormat="1" ht="12.95"/>
+    <row r="252" s="4" customFormat="1" ht="12.95"/>
+    <row r="253" s="4" customFormat="1" ht="12.95"/>
+    <row r="254" s="4" customFormat="1" ht="12.95"/>
+    <row r="255" s="4" customFormat="1" ht="12.95"/>
+    <row r="256" s="4" customFormat="1" ht="12.95"/>
+    <row r="257" s="4" customFormat="1" ht="12.95"/>
+    <row r="258" s="4" customFormat="1" ht="12.95"/>
+    <row r="259" s="4" customFormat="1" ht="12.95"/>
+    <row r="260" s="4" customFormat="1" ht="12.95"/>
+    <row r="261" s="4" customFormat="1" ht="12.95"/>
+    <row r="262" s="4" customFormat="1" ht="12.95"/>
+    <row r="263" s="4" customFormat="1" ht="12.95"/>
+    <row r="264" s="4" customFormat="1" ht="12.95"/>
+    <row r="265" s="4" customFormat="1" ht="12.95"/>
+    <row r="266" s="4" customFormat="1" ht="12.95"/>
+    <row r="267" s="4" customFormat="1" ht="12.95"/>
+    <row r="268" s="4" customFormat="1" ht="12.95"/>
+    <row r="269" s="4" customFormat="1" ht="12.95"/>
+    <row r="270" s="4" customFormat="1" ht="12.95"/>
+    <row r="271" s="4" customFormat="1" ht="12.95"/>
+    <row r="272" s="4" customFormat="1" ht="12.95"/>
+    <row r="273" s="4" customFormat="1" ht="12.95"/>
+    <row r="274" s="4" customFormat="1" ht="12.95"/>
+    <row r="275" s="4" customFormat="1" ht="12.95"/>
+    <row r="276" s="4" customFormat="1" ht="12.95"/>
+    <row r="277" s="4" customFormat="1" ht="12.95"/>
+    <row r="278" s="4" customFormat="1" ht="12.95"/>
+    <row r="279" s="4" customFormat="1" ht="12.95"/>
+    <row r="280" s="4" customFormat="1" ht="12.95"/>
+    <row r="281" s="4" customFormat="1" ht="12.95"/>
+    <row r="282" s="4" customFormat="1" ht="12.95"/>
+    <row r="283" s="4" customFormat="1" ht="12.95"/>
+    <row r="284" s="4" customFormat="1" ht="12.95"/>
+    <row r="285" s="4" customFormat="1" ht="12.95"/>
+    <row r="286" s="4" customFormat="1" ht="12.95"/>
+    <row r="287" s="4" customFormat="1" ht="12.95"/>
+    <row r="288" s="4" customFormat="1" ht="12.95"/>
+    <row r="289" s="4" customFormat="1" ht="12.95"/>
+    <row r="290" s="4" customFormat="1" ht="12.95"/>
+    <row r="291" s="4" customFormat="1" ht="12.95"/>
+    <row r="292" s="4" customFormat="1" ht="12.95"/>
+    <row r="293" s="4" customFormat="1" ht="12.95"/>
+    <row r="294" s="4" customFormat="1" ht="12.95"/>
+    <row r="295" s="4" customFormat="1" ht="12.95"/>
+    <row r="296" s="4" customFormat="1" ht="12.95"/>
+    <row r="297" s="4" customFormat="1" ht="12.95"/>
+    <row r="298" s="4" customFormat="1" ht="12.95"/>
+    <row r="299" s="4" customFormat="1" ht="12.95"/>
+    <row r="300" s="4" customFormat="1" ht="12.95"/>
+    <row r="301" s="4" customFormat="1" ht="12.95"/>
+    <row r="302" s="4" customFormat="1" ht="12.95"/>
+    <row r="303" s="4" customFormat="1" ht="12.95"/>
+    <row r="304" s="4" customFormat="1" ht="12.95"/>
+    <row r="305" s="4" customFormat="1" ht="12.95"/>
+    <row r="306" s="4" customFormat="1" ht="12.95"/>
+    <row r="307" s="4" customFormat="1" ht="12.95"/>
+    <row r="308" s="4" customFormat="1" ht="12.95"/>
+    <row r="309" s="4" customFormat="1" ht="12.95"/>
+    <row r="310" s="4" customFormat="1" ht="12.95"/>
+    <row r="311" s="4" customFormat="1" ht="12.95"/>
+    <row r="312" s="4" customFormat="1" ht="12.95"/>
+    <row r="313" s="4" customFormat="1" ht="12.95"/>
+    <row r="314" s="4" customFormat="1" ht="12.95"/>
+    <row r="315" s="4" customFormat="1" ht="12.95"/>
+    <row r="316" s="4" customFormat="1" ht="12.95"/>
+    <row r="317" s="4" customFormat="1" ht="12.95"/>
+    <row r="318" s="4" customFormat="1" ht="12.95"/>
+    <row r="319" s="4" customFormat="1" ht="12.95"/>
+    <row r="320" s="4" customFormat="1" ht="12.95"/>
+    <row r="321" s="4" customFormat="1" ht="12.95"/>
+    <row r="322" s="4" customFormat="1" ht="12.95"/>
+    <row r="323" s="4" customFormat="1" ht="12.95"/>
+    <row r="324" s="4" customFormat="1" ht="12.95"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1676,258 +1609,243 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E6DA48E-5363-4D00-97AD-0E6B6A5B44CA}">
-  <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" customWidth="1"/>
-    <col min="4" max="4" width="28.140625" customWidth="1"/>
-    <col min="5" max="5" width="27.28515625" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="4"/>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
-      <c r="D1" s="15">
-        <v>18</v>
-      </c>
-      <c r="E1" s="15">
-        <v>0.89800000000000002</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" s="15">
-        <v>1.6</v>
+      <c r="D1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="A2" s="4"/>
       <c r="B2" s="4"/>
-      <c r="C2" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="15">
+        <v>20.124999726027369</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.78452102304761584</v>
+      </c>
+      <c r="F2" s="4"/>
+      <c r="G2" s="15">
+        <v>1.6</v>
+      </c>
       <c r="H2" s="4"/>
-      <c r="I2" s="4" t="s">
-        <v>69</v>
-      </c>
+      <c r="I2" s="4"/>
       <c r="J2" s="4"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>71</v>
-      </c>
+      <c r="A3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="4"/>
       <c r="C3" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="H3" s="4"/>
-      <c r="I3" t="s">
-        <v>11</v>
+      <c r="I3" s="17" t="s">
+        <v>53</v>
       </c>
       <c r="J3" s="4"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" s="15">
-        <v>9</v>
-      </c>
-      <c r="D4" s="4">
-        <f>C4/$D$1</f>
-        <v>0.5</v>
-      </c>
-      <c r="E4" s="4">
-        <f>D4*$E$1</f>
-        <v>0.44900000000000001</v>
-      </c>
-      <c r="F4" s="15">
-        <v>8</v>
-      </c>
-      <c r="G4" s="4">
-        <f>F4/$G$1</f>
-        <v>5</v>
+      <c r="A4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="H4" s="4"/>
-      <c r="I4" s="4">
-        <f>E4/G4</f>
-        <v>8.9800000000000005E-2</v>
+      <c r="I4" t="s">
+        <v>60</v>
       </c>
       <c r="J4" s="4"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="16" t="s">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" s="15">
-        <v>6</v>
+        <v>62</v>
+      </c>
+      <c r="C5" s="18">
+        <f>12*0.25*(F5-5)</f>
+        <v>9</v>
       </c>
       <c r="D5" s="4">
-        <f>C5/$D$1</f>
-        <v>0.33333333333333331</v>
+        <f>C5/$D$2</f>
+        <v>0.44720497503214529</v>
       </c>
       <c r="E5" s="4">
-        <f>D5*$E$1</f>
-        <v>0.29933333333333334</v>
+        <f>D5*$E$2</f>
+        <v>0.3508417045242021</v>
       </c>
       <c r="F5" s="15">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G5" s="4">
-        <f>F5/$G$1</f>
-        <v>9.375</v>
+        <f>F5/$G$2</f>
+        <v>5</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4">
         <f>E5/G5</f>
-        <v>3.1928888888888889E-2</v>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="J5" s="4"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="15"/>
+        <v>63</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>64</v>
+      </c>
       <c r="C6" s="15">
-        <v>3209</v>
+        <v>6</v>
       </c>
       <c r="D6" s="4">
-        <f>C6/$D$1</f>
-        <v>178.27777777777777</v>
+        <f>C6/$D$2</f>
+        <v>0.29813665002143019</v>
       </c>
       <c r="E6" s="4">
-        <f>D6*$E$1</f>
-        <v>160.09344444444443</v>
+        <f>D6*$E$2</f>
+        <v>0.23389446968280142</v>
       </c>
       <c r="F6" s="15">
-        <v>600</v>
+        <v>15</v>
       </c>
       <c r="G6" s="4">
-        <f>F6/$G$1</f>
-        <v>375</v>
+        <f>F6/$G$2</f>
+        <v>9.375</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4">
         <f>E6/G6</f>
-        <v>0.42691585185185182</v>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="J6" s="4"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="B7" s="15"/>
       <c r="C7" s="15">
-        <v>5</v>
+        <v>3209</v>
       </c>
       <c r="D7" s="4">
-        <f>C7/$D$1</f>
-        <v>0.27777777777777779</v>
+        <f>C7/$D$2</f>
+        <v>159.45341831979491</v>
       </c>
       <c r="E7" s="4">
-        <f>D7*$E$1</f>
-        <v>0.24944444444444447</v>
+        <f>D7*$E$2</f>
+        <v>125.09455886868496</v>
       </c>
       <c r="F7" s="15">
-        <v>20</v>
+        <v>600</v>
       </c>
       <c r="G7" s="4">
-        <f>F7/$G$1</f>
-        <v>12.5</v>
+        <f>F7/$G$2</f>
+        <v>375</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4">
         <f>E7/G7</f>
-        <v>1.9955555555555556E-2</v>
+        <v>0.33358549031649321</v>
       </c>
       <c r="J7" s="4"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="15">
         <v>6</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15">
-        <v>0</v>
-      </c>
       <c r="D8" s="4">
-        <f>C8/$D$1</f>
-        <v>0</v>
+        <f>C8/$D$2</f>
+        <v>0.29813665002143019</v>
       </c>
       <c r="E8" s="4">
-        <f>D8*$E$1</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="15"/>
+        <f>D8*$E$2</f>
+        <v>0.23389446968280142</v>
+      </c>
+      <c r="F8" s="15">
+        <v>20</v>
+      </c>
       <c r="G8" s="4">
-        <f>F8/$G$1</f>
-        <v>0</v>
+        <f>F8/$G$2</f>
+        <v>12.5</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4">
-        <v>0</v>
+        <f>E8/G8</f>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="J8" s="4"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="16" t="s">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="15">
         <v>0</v>
       </c>
       <c r="D9" s="4">
-        <f>C9/$D$1</f>
+        <f>C9/$D$2</f>
         <v>0</v>
       </c>
       <c r="E9" s="4">
-        <f>D9*$E$1</f>
+        <f>D9*$E$2</f>
         <v>0</v>
       </c>
       <c r="F9" s="15"/>
       <c r="G9" s="4">
-        <f>F9/$G$1</f>
+        <f>F9/$G$2</f>
         <v>0</v>
       </c>
       <c r="H9" s="4"/>
@@ -1937,11 +1855,39 @@
       <c r="J9" s="4"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="B10" s="3"/>
-      <c r="D10" s="3"/>
+      <c r="A10" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4">
+        <f>C10/$D$2</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="4">
+        <f>D10*$E$2</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="15"/>
+      <c r="G10" s="4">
+        <f>F10/$G$2</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="3"/>
+      <c r="D11" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1950,16 +1896,16 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AF7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:AZ7"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.28515625" customWidth="1"/>
     <col min="2" max="3" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32">
+    <row r="1" spans="1:52">
       <c r="A1" t="s">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="B1" s="2">
         <v>2020</v>
@@ -2054,775 +2000,1316 @@
       <c r="AF1" s="2">
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:32">
+      <c r="AG1" s="2">
+        <v>2051</v>
+      </c>
+      <c r="AH1" s="2">
+        <v>2052</v>
+      </c>
+      <c r="AI1" s="2">
+        <v>2053</v>
+      </c>
+      <c r="AJ1" s="2">
+        <v>2054</v>
+      </c>
+      <c r="AK1" s="2">
+        <v>2055</v>
+      </c>
+      <c r="AL1" s="2">
+        <v>2056</v>
+      </c>
+      <c r="AM1" s="2">
+        <v>2057</v>
+      </c>
+      <c r="AN1" s="2">
+        <v>2058</v>
+      </c>
+      <c r="AO1" s="2">
+        <v>2059</v>
+      </c>
+      <c r="AP1" s="2">
+        <v>2060</v>
+      </c>
+      <c r="AQ1" s="2">
+        <v>2061</v>
+      </c>
+      <c r="AR1" s="2">
+        <v>2062</v>
+      </c>
+      <c r="AS1" s="2">
+        <v>2063</v>
+      </c>
+      <c r="AT1" s="2">
+        <v>2064</v>
+      </c>
+      <c r="AU1" s="2">
+        <v>2065</v>
+      </c>
+      <c r="AV1" s="2">
+        <v>2066</v>
+      </c>
+      <c r="AW1" s="2">
+        <v>2067</v>
+      </c>
+      <c r="AX1" s="2">
+        <v>2068</v>
+      </c>
+      <c r="AY1" s="2">
+        <v>2069</v>
+      </c>
+      <c r="AZ1" s="2">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52">
       <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="B2" s="3">
+        <f>Calcs!I5</f>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="C2">
-        <f>B2</f>
-        <v>0</v>
+        <f t="shared" ref="C2:AF2" si="0">B2</f>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="D2">
-        <f>C2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="E2">
-        <f>D2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="F2">
-        <f>E2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="G2">
-        <f>F2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="H2">
-        <f>G2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="I2">
-        <f>H2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="J2">
-        <f>I2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="K2">
-        <f>J2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="L2">
-        <f>K2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="M2">
-        <f>L2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="N2">
-        <f>M2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="O2">
-        <f>N2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="P2">
-        <f>O2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="Q2">
-        <f>P2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="R2">
-        <f>Q2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="S2">
-        <f>R2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="T2">
-        <f>S2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="U2">
-        <f>T2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="V2">
-        <f>U2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="W2">
-        <f>V2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="X2">
-        <f>W2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="Y2">
-        <f>X2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="Z2">
-        <f>Y2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="AA2">
-        <f>Z2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="AB2">
-        <f>AA2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="AC2">
-        <f>AB2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="AD2">
-        <f>AC2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="AE2">
-        <f>AD2</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>7.0168340904840421E-2</v>
       </c>
       <c r="AF2">
-        <f>AE2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32">
+        <f t="shared" si="0"/>
+        <v>7.0168340904840421E-2</v>
+      </c>
+      <c r="AG2">
+        <f t="shared" ref="AG2:AG7" si="1">AF2</f>
+        <v>7.0168340904840421E-2</v>
+      </c>
+      <c r="AH2">
+        <f t="shared" ref="AH2:AH7" si="2">AG2</f>
+        <v>7.0168340904840421E-2</v>
+      </c>
+      <c r="AI2">
+        <f t="shared" ref="AI2:AI7" si="3">AH2</f>
+        <v>7.0168340904840421E-2</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" ref="AJ2:AJ7" si="4">AI2</f>
+        <v>7.0168340904840421E-2</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" ref="AK2:AK7" si="5">AJ2</f>
+        <v>7.0168340904840421E-2</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" ref="AL2:AL7" si="6">AK2</f>
+        <v>7.0168340904840421E-2</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" ref="AM2:AM7" si="7">AL2</f>
+        <v>7.0168340904840421E-2</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" ref="AN2:AN7" si="8">AM2</f>
+        <v>7.0168340904840421E-2</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" ref="AO2:AO7" si="9">AN2</f>
+        <v>7.0168340904840421E-2</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" ref="AP2:AP7" si="10">AO2</f>
+        <v>7.0168340904840421E-2</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" ref="AQ2:AQ7" si="11">AP2</f>
+        <v>7.0168340904840421E-2</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" ref="AR2:AR7" si="12">AQ2</f>
+        <v>7.0168340904840421E-2</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" ref="AS2:AS7" si="13">AR2</f>
+        <v>7.0168340904840421E-2</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" ref="AT2:AT7" si="14">AS2</f>
+        <v>7.0168340904840421E-2</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" ref="AU2:AU7" si="15">AT2</f>
+        <v>7.0168340904840421E-2</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" ref="AV2:AV7" si="16">AU2</f>
+        <v>7.0168340904840421E-2</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" ref="AW2:AW7" si="17">AV2</f>
+        <v>7.0168340904840421E-2</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" ref="AX2:AX7" si="18">AW2</f>
+        <v>7.0168340904840421E-2</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" ref="AY2:AY7" si="19">AX2</f>
+        <v>7.0168340904840421E-2</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" ref="AZ2:AZ7" si="20">AY2</f>
+        <v>7.0168340904840421E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="B3" s="3">
-        <f>Calcs!I5</f>
-        <v>3.1928888888888889E-2</v>
+        <f>Calcs!I6</f>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="C3" s="3">
-        <f>B3</f>
-        <v>3.1928888888888889E-2</v>
+        <f t="shared" ref="C3:AF3" si="21">B3</f>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="D3" s="3">
-        <f>C3</f>
-        <v>3.1928888888888889E-2</v>
+        <f t="shared" si="21"/>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="E3" s="3">
-        <f>D3</f>
-        <v>3.1928888888888889E-2</v>
+        <f t="shared" si="21"/>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="F3" s="3">
-        <f>E3</f>
-        <v>3.1928888888888889E-2</v>
+        <f t="shared" si="21"/>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="G3" s="3">
-        <f>F3</f>
-        <v>3.1928888888888889E-2</v>
+        <f t="shared" si="21"/>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="H3" s="3">
-        <f>G3</f>
-        <v>3.1928888888888889E-2</v>
+        <f t="shared" si="21"/>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="I3" s="3">
-        <f>H3</f>
-        <v>3.1928888888888889E-2</v>
+        <f t="shared" si="21"/>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="J3" s="3">
-        <f>I3</f>
-        <v>3.1928888888888889E-2</v>
+        <f t="shared" si="21"/>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="K3" s="3">
-        <f>J3</f>
-        <v>3.1928888888888889E-2</v>
+        <f t="shared" si="21"/>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="L3" s="3">
-        <f>K3</f>
-        <v>3.1928888888888889E-2</v>
+        <f t="shared" si="21"/>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="M3" s="3">
-        <f>L3</f>
-        <v>3.1928888888888889E-2</v>
+        <f t="shared" si="21"/>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="N3" s="3">
-        <f>M3</f>
-        <v>3.1928888888888889E-2</v>
+        <f t="shared" si="21"/>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="O3" s="3">
-        <f>N3</f>
-        <v>3.1928888888888889E-2</v>
+        <f t="shared" si="21"/>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="P3" s="3">
-        <f>O3</f>
-        <v>3.1928888888888889E-2</v>
+        <f t="shared" si="21"/>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="Q3" s="3">
-        <f>P3</f>
-        <v>3.1928888888888889E-2</v>
+        <f t="shared" si="21"/>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="R3" s="3">
-        <f>Q3</f>
-        <v>3.1928888888888889E-2</v>
+        <f t="shared" si="21"/>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="S3" s="3">
-        <f>R3</f>
-        <v>3.1928888888888889E-2</v>
+        <f t="shared" si="21"/>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="T3" s="3">
-        <f>S3</f>
-        <v>3.1928888888888889E-2</v>
+        <f t="shared" si="21"/>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="U3" s="3">
-        <f>T3</f>
-        <v>3.1928888888888889E-2</v>
+        <f t="shared" si="21"/>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="V3" s="3">
-        <f>U3</f>
-        <v>3.1928888888888889E-2</v>
+        <f t="shared" si="21"/>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="W3" s="3">
-        <f>V3</f>
-        <v>3.1928888888888889E-2</v>
+        <f t="shared" si="21"/>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="X3" s="3">
-        <f>W3</f>
-        <v>3.1928888888888889E-2</v>
+        <f t="shared" si="21"/>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="Y3" s="3">
-        <f>X3</f>
-        <v>3.1928888888888889E-2</v>
+        <f t="shared" si="21"/>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="Z3" s="3">
-        <f>Y3</f>
-        <v>3.1928888888888889E-2</v>
+        <f t="shared" si="21"/>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="AA3" s="3">
-        <f>Z3</f>
-        <v>3.1928888888888889E-2</v>
+        <f t="shared" si="21"/>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="AB3" s="3">
-        <f>AA3</f>
-        <v>3.1928888888888889E-2</v>
+        <f t="shared" si="21"/>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="AC3" s="3">
-        <f>AB3</f>
-        <v>3.1928888888888889E-2</v>
+        <f t="shared" si="21"/>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="AD3" s="3">
-        <f>AC3</f>
-        <v>3.1928888888888889E-2</v>
+        <f t="shared" si="21"/>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="AE3" s="3">
-        <f>AD3</f>
-        <v>3.1928888888888889E-2</v>
+        <f t="shared" si="21"/>
+        <v>2.4948743432832151E-2</v>
       </c>
       <c r="AF3" s="3">
-        <f>AE3</f>
-        <v>3.1928888888888889E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32">
+        <f t="shared" si="21"/>
+        <v>2.4948743432832151E-2</v>
+      </c>
+      <c r="AG3" s="3">
+        <f t="shared" si="1"/>
+        <v>2.4948743432832151E-2</v>
+      </c>
+      <c r="AH3" s="3">
+        <f t="shared" si="2"/>
+        <v>2.4948743432832151E-2</v>
+      </c>
+      <c r="AI3" s="3">
+        <f t="shared" si="3"/>
+        <v>2.4948743432832151E-2</v>
+      </c>
+      <c r="AJ3" s="3">
+        <f t="shared" si="4"/>
+        <v>2.4948743432832151E-2</v>
+      </c>
+      <c r="AK3" s="3">
+        <f t="shared" si="5"/>
+        <v>2.4948743432832151E-2</v>
+      </c>
+      <c r="AL3" s="3">
+        <f t="shared" si="6"/>
+        <v>2.4948743432832151E-2</v>
+      </c>
+      <c r="AM3" s="3">
+        <f t="shared" si="7"/>
+        <v>2.4948743432832151E-2</v>
+      </c>
+      <c r="AN3" s="3">
+        <f t="shared" si="8"/>
+        <v>2.4948743432832151E-2</v>
+      </c>
+      <c r="AO3" s="3">
+        <f t="shared" si="9"/>
+        <v>2.4948743432832151E-2</v>
+      </c>
+      <c r="AP3" s="3">
+        <f t="shared" si="10"/>
+        <v>2.4948743432832151E-2</v>
+      </c>
+      <c r="AQ3" s="3">
+        <f t="shared" si="11"/>
+        <v>2.4948743432832151E-2</v>
+      </c>
+      <c r="AR3" s="3">
+        <f t="shared" si="12"/>
+        <v>2.4948743432832151E-2</v>
+      </c>
+      <c r="AS3" s="3">
+        <f t="shared" si="13"/>
+        <v>2.4948743432832151E-2</v>
+      </c>
+      <c r="AT3" s="3">
+        <f t="shared" si="14"/>
+        <v>2.4948743432832151E-2</v>
+      </c>
+      <c r="AU3" s="3">
+        <f t="shared" si="15"/>
+        <v>2.4948743432832151E-2</v>
+      </c>
+      <c r="AV3" s="3">
+        <f t="shared" si="16"/>
+        <v>2.4948743432832151E-2</v>
+      </c>
+      <c r="AW3" s="3">
+        <f t="shared" si="17"/>
+        <v>2.4948743432832151E-2</v>
+      </c>
+      <c r="AX3" s="3">
+        <f t="shared" si="18"/>
+        <v>2.4948743432832151E-2</v>
+      </c>
+      <c r="AY3" s="3">
+        <f t="shared" si="19"/>
+        <v>2.4948743432832151E-2</v>
+      </c>
+      <c r="AZ3" s="3">
+        <f t="shared" si="20"/>
+        <v>2.4948743432832151E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="B4" s="3">
-        <f>Calcs!I6</f>
-        <v>0.42691585185185182</v>
+        <f>Calcs!I7</f>
+        <v>0.33358549031649321</v>
       </c>
       <c r="C4" s="3">
-        <f>B4</f>
-        <v>0.42691585185185182</v>
+        <f t="shared" ref="C4:AF4" si="22">B4</f>
+        <v>0.33358549031649321</v>
       </c>
       <c r="D4" s="3">
-        <f>C4</f>
-        <v>0.42691585185185182</v>
+        <f t="shared" si="22"/>
+        <v>0.33358549031649321</v>
       </c>
       <c r="E4" s="3">
-        <f>D4</f>
-        <v>0.42691585185185182</v>
+        <f t="shared" si="22"/>
+        <v>0.33358549031649321</v>
       </c>
       <c r="F4" s="3">
-        <f>E4</f>
-        <v>0.42691585185185182</v>
+        <f t="shared" si="22"/>
+        <v>0.33358549031649321</v>
       </c>
       <c r="G4" s="3">
-        <f>F4</f>
-        <v>0.42691585185185182</v>
+        <f t="shared" si="22"/>
+        <v>0.33358549031649321</v>
       </c>
       <c r="H4" s="3">
-        <f>G4</f>
-        <v>0.42691585185185182</v>
+        <f t="shared" si="22"/>
+        <v>0.33358549031649321</v>
       </c>
       <c r="I4" s="3">
-        <f>H4</f>
-        <v>0.42691585185185182</v>
+        <f t="shared" si="22"/>
+        <v>0.33358549031649321</v>
       </c>
       <c r="J4" s="3">
-        <f>I4</f>
-        <v>0.42691585185185182</v>
+        <f t="shared" si="22"/>
+        <v>0.33358549031649321</v>
       </c>
       <c r="K4" s="3">
-        <f>J4</f>
-        <v>0.42691585185185182</v>
+        <f t="shared" si="22"/>
+        <v>0.33358549031649321</v>
       </c>
       <c r="L4" s="3">
-        <f>K4</f>
-        <v>0.42691585185185182</v>
+        <f t="shared" si="22"/>
+        <v>0.33358549031649321</v>
       </c>
       <c r="M4" s="3">
-        <f>L4</f>
-        <v>0.42691585185185182</v>
+        <f t="shared" si="22"/>
+        <v>0.33358549031649321</v>
       </c>
       <c r="N4" s="3">
-        <f>M4</f>
-        <v>0.42691585185185182</v>
+        <f t="shared" si="22"/>
+        <v>0.33358549031649321</v>
       </c>
       <c r="O4" s="3">
-        <f>N4</f>
-        <v>0.42691585185185182</v>
+        <f t="shared" si="22"/>
+        <v>0.33358549031649321</v>
       </c>
       <c r="P4" s="3">
-        <f>O4</f>
-        <v>0.42691585185185182</v>
+        <f t="shared" si="22"/>
+        <v>0.33358549031649321</v>
       </c>
       <c r="Q4" s="3">
-        <f>P4</f>
-        <v>0.42691585185185182</v>
+        <f t="shared" si="22"/>
+        <v>0.33358549031649321</v>
       </c>
       <c r="R4" s="3">
-        <f>Q4</f>
-        <v>0.42691585185185182</v>
+        <f t="shared" si="22"/>
+        <v>0.33358549031649321</v>
       </c>
       <c r="S4" s="3">
-        <f>R4</f>
-        <v>0.42691585185185182</v>
+        <f t="shared" si="22"/>
+        <v>0.33358549031649321</v>
       </c>
       <c r="T4" s="3">
-        <f>S4</f>
-        <v>0.42691585185185182</v>
+        <f t="shared" si="22"/>
+        <v>0.33358549031649321</v>
       </c>
       <c r="U4" s="3">
-        <f>T4</f>
-        <v>0.42691585185185182</v>
+        <f t="shared" si="22"/>
+        <v>0.33358549031649321</v>
       </c>
       <c r="V4" s="3">
-        <f>U4</f>
-        <v>0.42691585185185182</v>
+        <f t="shared" si="22"/>
+        <v>0.33358549031649321</v>
       </c>
       <c r="W4" s="3">
-        <f>V4</f>
-        <v>0.42691585185185182</v>
+        <f t="shared" si="22"/>
+        <v>0.33358549031649321</v>
       </c>
       <c r="X4" s="3">
-        <f>W4</f>
-        <v>0.42691585185185182</v>
+        <f t="shared" si="22"/>
+        <v>0.33358549031649321</v>
       </c>
       <c r="Y4" s="3">
-        <f>X4</f>
-        <v>0.42691585185185182</v>
+        <f t="shared" si="22"/>
+        <v>0.33358549031649321</v>
       </c>
       <c r="Z4" s="3">
-        <f>Y4</f>
-        <v>0.42691585185185182</v>
+        <f t="shared" si="22"/>
+        <v>0.33358549031649321</v>
       </c>
       <c r="AA4" s="3">
-        <f>Z4</f>
-        <v>0.42691585185185182</v>
+        <f t="shared" si="22"/>
+        <v>0.33358549031649321</v>
       </c>
       <c r="AB4" s="3">
-        <f>AA4</f>
-        <v>0.42691585185185182</v>
+        <f t="shared" si="22"/>
+        <v>0.33358549031649321</v>
       </c>
       <c r="AC4" s="3">
-        <f>AB4</f>
-        <v>0.42691585185185182</v>
+        <f t="shared" si="22"/>
+        <v>0.33358549031649321</v>
       </c>
       <c r="AD4" s="3">
-        <f>AC4</f>
-        <v>0.42691585185185182</v>
+        <f t="shared" si="22"/>
+        <v>0.33358549031649321</v>
       </c>
       <c r="AE4" s="3">
-        <f>AD4</f>
-        <v>0.42691585185185182</v>
+        <f t="shared" si="22"/>
+        <v>0.33358549031649321</v>
       </c>
       <c r="AF4" s="3">
-        <f>AE4</f>
-        <v>0.42691585185185182</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32">
+        <f t="shared" si="22"/>
+        <v>0.33358549031649321</v>
+      </c>
+      <c r="AG4" s="3">
+        <f t="shared" si="1"/>
+        <v>0.33358549031649321</v>
+      </c>
+      <c r="AH4" s="3">
+        <f t="shared" si="2"/>
+        <v>0.33358549031649321</v>
+      </c>
+      <c r="AI4" s="3">
+        <f t="shared" si="3"/>
+        <v>0.33358549031649321</v>
+      </c>
+      <c r="AJ4" s="3">
+        <f t="shared" si="4"/>
+        <v>0.33358549031649321</v>
+      </c>
+      <c r="AK4" s="3">
+        <f t="shared" si="5"/>
+        <v>0.33358549031649321</v>
+      </c>
+      <c r="AL4" s="3">
+        <f t="shared" si="6"/>
+        <v>0.33358549031649321</v>
+      </c>
+      <c r="AM4" s="3">
+        <f t="shared" si="7"/>
+        <v>0.33358549031649321</v>
+      </c>
+      <c r="AN4" s="3">
+        <f t="shared" si="8"/>
+        <v>0.33358549031649321</v>
+      </c>
+      <c r="AO4" s="3">
+        <f t="shared" si="9"/>
+        <v>0.33358549031649321</v>
+      </c>
+      <c r="AP4" s="3">
+        <f t="shared" si="10"/>
+        <v>0.33358549031649321</v>
+      </c>
+      <c r="AQ4" s="3">
+        <f t="shared" si="11"/>
+        <v>0.33358549031649321</v>
+      </c>
+      <c r="AR4" s="3">
+        <f t="shared" si="12"/>
+        <v>0.33358549031649321</v>
+      </c>
+      <c r="AS4" s="3">
+        <f t="shared" si="13"/>
+        <v>0.33358549031649321</v>
+      </c>
+      <c r="AT4" s="3">
+        <f t="shared" si="14"/>
+        <v>0.33358549031649321</v>
+      </c>
+      <c r="AU4" s="3">
+        <f t="shared" si="15"/>
+        <v>0.33358549031649321</v>
+      </c>
+      <c r="AV4" s="3">
+        <f t="shared" si="16"/>
+        <v>0.33358549031649321</v>
+      </c>
+      <c r="AW4" s="3">
+        <f t="shared" si="17"/>
+        <v>0.33358549031649321</v>
+      </c>
+      <c r="AX4" s="3">
+        <f t="shared" si="18"/>
+        <v>0.33358549031649321</v>
+      </c>
+      <c r="AY4" s="3">
+        <f t="shared" si="19"/>
+        <v>0.33358549031649321</v>
+      </c>
+      <c r="AZ4" s="3">
+        <f t="shared" si="20"/>
+        <v>0.33358549031649321</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="B5" s="3">
-        <f>Calcs!I7</f>
-        <v>1.9955555555555556E-2</v>
+        <f>Calcs!I8</f>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="C5" s="3">
-        <f>B5</f>
-        <v>1.9955555555555556E-2</v>
+        <f t="shared" ref="C5:AF5" si="23">B5</f>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="D5" s="3">
-        <f>C5</f>
-        <v>1.9955555555555556E-2</v>
+        <f t="shared" si="23"/>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="E5" s="3">
-        <f>D5</f>
-        <v>1.9955555555555556E-2</v>
+        <f t="shared" si="23"/>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="F5" s="3">
-        <f>E5</f>
-        <v>1.9955555555555556E-2</v>
+        <f t="shared" si="23"/>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="G5" s="3">
-        <f>F5</f>
-        <v>1.9955555555555556E-2</v>
+        <f t="shared" si="23"/>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="H5" s="3">
-        <f>G5</f>
-        <v>1.9955555555555556E-2</v>
+        <f t="shared" si="23"/>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="I5" s="3">
-        <f>H5</f>
-        <v>1.9955555555555556E-2</v>
+        <f t="shared" si="23"/>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="J5" s="3">
-        <f>I5</f>
-        <v>1.9955555555555556E-2</v>
+        <f t="shared" si="23"/>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="K5" s="3">
-        <f>J5</f>
-        <v>1.9955555555555556E-2</v>
+        <f t="shared" si="23"/>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="L5" s="3">
-        <f>K5</f>
-        <v>1.9955555555555556E-2</v>
+        <f t="shared" si="23"/>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="M5" s="3">
-        <f>L5</f>
-        <v>1.9955555555555556E-2</v>
+        <f t="shared" si="23"/>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="N5" s="3">
-        <f>M5</f>
-        <v>1.9955555555555556E-2</v>
+        <f t="shared" si="23"/>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="O5" s="3">
-        <f>N5</f>
-        <v>1.9955555555555556E-2</v>
+        <f t="shared" si="23"/>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="P5" s="3">
-        <f>O5</f>
-        <v>1.9955555555555556E-2</v>
+        <f t="shared" si="23"/>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="Q5" s="3">
-        <f>P5</f>
-        <v>1.9955555555555556E-2</v>
+        <f t="shared" si="23"/>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="R5" s="3">
-        <f>Q5</f>
-        <v>1.9955555555555556E-2</v>
+        <f t="shared" si="23"/>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="S5" s="3">
-        <f>R5</f>
-        <v>1.9955555555555556E-2</v>
+        <f t="shared" si="23"/>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="T5" s="3">
-        <f>S5</f>
-        <v>1.9955555555555556E-2</v>
+        <f t="shared" si="23"/>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="U5" s="3">
-        <f>T5</f>
-        <v>1.9955555555555556E-2</v>
+        <f t="shared" si="23"/>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="V5" s="3">
-        <f>U5</f>
-        <v>1.9955555555555556E-2</v>
+        <f t="shared" si="23"/>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="W5" s="3">
-        <f>V5</f>
-        <v>1.9955555555555556E-2</v>
+        <f t="shared" si="23"/>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="X5" s="3">
-        <f>W5</f>
-        <v>1.9955555555555556E-2</v>
+        <f t="shared" si="23"/>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="Y5" s="3">
-        <f>X5</f>
-        <v>1.9955555555555556E-2</v>
+        <f t="shared" si="23"/>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="Z5" s="3">
-        <f>Y5</f>
-        <v>1.9955555555555556E-2</v>
+        <f t="shared" si="23"/>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="AA5" s="3">
-        <f>Z5</f>
-        <v>1.9955555555555556E-2</v>
+        <f t="shared" si="23"/>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="AB5" s="3">
-        <f>AA5</f>
-        <v>1.9955555555555556E-2</v>
+        <f t="shared" si="23"/>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="AC5" s="3">
-        <f>AB5</f>
-        <v>1.9955555555555556E-2</v>
+        <f t="shared" si="23"/>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="AD5" s="3">
-        <f>AC5</f>
-        <v>1.9955555555555556E-2</v>
+        <f t="shared" si="23"/>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="AE5" s="3">
-        <f>AD5</f>
-        <v>1.9955555555555556E-2</v>
+        <f t="shared" si="23"/>
+        <v>1.8711557574624112E-2</v>
       </c>
       <c r="AF5" s="3">
-        <f>AE5</f>
-        <v>1.9955555555555556E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32">
+        <f t="shared" si="23"/>
+        <v>1.8711557574624112E-2</v>
+      </c>
+      <c r="AG5" s="3">
+        <f t="shared" si="1"/>
+        <v>1.8711557574624112E-2</v>
+      </c>
+      <c r="AH5" s="3">
+        <f t="shared" si="2"/>
+        <v>1.8711557574624112E-2</v>
+      </c>
+      <c r="AI5" s="3">
+        <f t="shared" si="3"/>
+        <v>1.8711557574624112E-2</v>
+      </c>
+      <c r="AJ5" s="3">
+        <f t="shared" si="4"/>
+        <v>1.8711557574624112E-2</v>
+      </c>
+      <c r="AK5" s="3">
+        <f t="shared" si="5"/>
+        <v>1.8711557574624112E-2</v>
+      </c>
+      <c r="AL5" s="3">
+        <f t="shared" si="6"/>
+        <v>1.8711557574624112E-2</v>
+      </c>
+      <c r="AM5" s="3">
+        <f t="shared" si="7"/>
+        <v>1.8711557574624112E-2</v>
+      </c>
+      <c r="AN5" s="3">
+        <f t="shared" si="8"/>
+        <v>1.8711557574624112E-2</v>
+      </c>
+      <c r="AO5" s="3">
+        <f t="shared" si="9"/>
+        <v>1.8711557574624112E-2</v>
+      </c>
+      <c r="AP5" s="3">
+        <f t="shared" si="10"/>
+        <v>1.8711557574624112E-2</v>
+      </c>
+      <c r="AQ5" s="3">
+        <f t="shared" si="11"/>
+        <v>1.8711557574624112E-2</v>
+      </c>
+      <c r="AR5" s="3">
+        <f t="shared" si="12"/>
+        <v>1.8711557574624112E-2</v>
+      </c>
+      <c r="AS5" s="3">
+        <f t="shared" si="13"/>
+        <v>1.8711557574624112E-2</v>
+      </c>
+      <c r="AT5" s="3">
+        <f t="shared" si="14"/>
+        <v>1.8711557574624112E-2</v>
+      </c>
+      <c r="AU5" s="3">
+        <f t="shared" si="15"/>
+        <v>1.8711557574624112E-2</v>
+      </c>
+      <c r="AV5" s="3">
+        <f t="shared" si="16"/>
+        <v>1.8711557574624112E-2</v>
+      </c>
+      <c r="AW5" s="3">
+        <f t="shared" si="17"/>
+        <v>1.8711557574624112E-2</v>
+      </c>
+      <c r="AX5" s="3">
+        <f t="shared" si="18"/>
+        <v>1.8711557574624112E-2</v>
+      </c>
+      <c r="AY5" s="3">
+        <f t="shared" si="19"/>
+        <v>1.8711557574624112E-2</v>
+      </c>
+      <c r="AZ5" s="3">
+        <f t="shared" si="20"/>
+        <v>1.8711557574624112E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6">
-        <f>B6</f>
+        <f t="shared" ref="C6:AF6" si="24">B6</f>
         <v>0</v>
       </c>
       <c r="D6">
-        <f>C6</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="E6">
-        <f>D6</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F6">
-        <f>E6</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="G6">
-        <f>F6</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H6">
-        <f>G6</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="I6">
-        <f>H6</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="J6">
-        <f>I6</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="K6">
-        <f>J6</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="L6">
-        <f>K6</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="M6">
-        <f>L6</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="N6">
-        <f>M6</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="O6">
-        <f>N6</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="P6">
-        <f>O6</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="Q6">
-        <f>P6</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="R6">
-        <f>Q6</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="S6">
-        <f>R6</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="T6">
-        <f>S6</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="U6">
-        <f>T6</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="V6">
-        <f>U6</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="W6">
-        <f>V6</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="X6">
-        <f>W6</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="Y6">
-        <f>X6</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="Z6">
-        <f>Y6</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AA6">
-        <f>Z6</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AB6">
-        <f>AA6</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AC6">
-        <f>AB6</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AD6">
-        <f>AC6</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AE6">
-        <f>AD6</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="AF6">
-        <f>AE6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <f>B7</f>
+        <f t="shared" ref="C7:AF7" si="25">B7</f>
         <v>0</v>
       </c>
       <c r="D7">
-        <f>C7</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E7">
-        <f>D7</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="F7">
-        <f>E7</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="G7">
-        <f>F7</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H7">
-        <f>G7</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="I7">
-        <f>H7</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="J7">
-        <f>I7</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="K7">
-        <f>J7</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="L7">
-        <f>K7</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M7">
-        <f>L7</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="N7">
-        <f>M7</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="O7">
-        <f>N7</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="P7">
-        <f>O7</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="Q7">
-        <f>P7</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="R7">
-        <f>Q7</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="S7">
-        <f>R7</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="T7">
-        <f>S7</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="U7">
-        <f>T7</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="V7">
-        <f>U7</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="W7">
-        <f>V7</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="X7">
-        <f>W7</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="Y7">
-        <f>X7</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="Z7">
-        <f>Y7</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AA7">
-        <f>Z7</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AB7">
-        <f>AA7</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC7">
-        <f>AB7</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AD7">
-        <f>AC7</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AE7">
-        <f>AD7</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AF7">
-        <f>AE7</f>
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -2836,16 +3323,16 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AF7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:AZ7"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.28515625" customWidth="1"/>
     <col min="2" max="3" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32">
+    <row r="1" spans="1:52">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="B1" s="2">
         <v>2020</v>
@@ -2940,10 +3427,70 @@
       <c r="AF1" s="2">
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:32">
+      <c r="AG1" s="2">
+        <v>2051</v>
+      </c>
+      <c r="AH1" s="2">
+        <v>2052</v>
+      </c>
+      <c r="AI1" s="2">
+        <v>2053</v>
+      </c>
+      <c r="AJ1" s="2">
+        <v>2054</v>
+      </c>
+      <c r="AK1" s="2">
+        <v>2055</v>
+      </c>
+      <c r="AL1" s="2">
+        <v>2056</v>
+      </c>
+      <c r="AM1" s="2">
+        <v>2057</v>
+      </c>
+      <c r="AN1" s="2">
+        <v>2058</v>
+      </c>
+      <c r="AO1" s="2">
+        <v>2059</v>
+      </c>
+      <c r="AP1" s="2">
+        <v>2060</v>
+      </c>
+      <c r="AQ1" s="2">
+        <v>2061</v>
+      </c>
+      <c r="AR1" s="2">
+        <v>2062</v>
+      </c>
+      <c r="AS1" s="2">
+        <v>2063</v>
+      </c>
+      <c r="AT1" s="2">
+        <v>2064</v>
+      </c>
+      <c r="AU1" s="2">
+        <v>2065</v>
+      </c>
+      <c r="AV1" s="2">
+        <v>2066</v>
+      </c>
+      <c r="AW1" s="2">
+        <v>2067</v>
+      </c>
+      <c r="AX1" s="2">
+        <v>2068</v>
+      </c>
+      <c r="AY1" s="2">
+        <v>2069</v>
+      </c>
+      <c r="AZ1" s="2">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -3038,10 +3585,70 @@
       <c r="AF2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:32">
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>0</v>
+      </c>
+      <c r="AP2">
+        <v>0</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+      <c r="AR2">
+        <v>0</v>
+      </c>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+      <c r="AT2">
+        <v>0</v>
+      </c>
+      <c r="AU2">
+        <v>0</v>
+      </c>
+      <c r="AV2">
+        <v>0</v>
+      </c>
+      <c r="AW2">
+        <v>0</v>
+      </c>
+      <c r="AX2">
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <v>0</v>
+      </c>
+      <c r="AZ2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3136,10 +3743,70 @@
       <c r="AF3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:32">
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -3234,10 +3901,70 @@
       <c r="AF4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:32">
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3332,10 +4059,70 @@
       <c r="AF5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:32">
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3430,10 +4217,70 @@
       <c r="AF6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:32">
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3526,10 +4373,241 @@
         <v>0</v>
       </c>
       <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
+    <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="79748b23-d81a-423e-9112-21109dc864e6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F9CF3FA-7567-464B-BF07-C0367C9C26D2}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD11A772-104E-4656-9BED-4681E1504AD1}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2575661-C557-4BD8-9D9A-DA5E7AF36563}"/>
 </file>